--- a/risorse/Risorsa_19_Order_to_Cash_AI.xlsx
+++ b/risorse/Risorsa_19_Order_to_Cash_AI.xlsx
@@ -18,10 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="€ #,##0;-"/>
-  </numFmts>
-  <fonts count="5">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,29 +28,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="0000838F"/>
-      <sz val="11"/>
+      <color rgb="00777777"/>
+      <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
+      <color rgb="001E3A5F"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,16 +61,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000BCD4"/>
+        <fgColor rgb="001E3A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000A1F2E"/>
+        <fgColor rgb="00E8F4FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -78,46 +83,37 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CFD8DC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CFD8DC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CFD8DC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CFD8DC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,30 +483,30 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AIOsha · Risorsa 19 — Order-to-Cash AI per B2B/Manifattura</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>AI Osha — Risorsa 19 · Order-to-Cash con l'AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mappa di 12 soluzioni + fasce prezzo + dimensione PMI ideale</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
+          <t>Mappa di 12 soluzioni con fasce di prezzo e dimensione aziendale ideale. Per B2B e manifattura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Soluzione</t>
@@ -523,7 +519,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Target PMI (dipendenti)</t>
+          <t>Target (dipendenti)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -547,7 +543,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="52" customHeight="1">
+    <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Esker</t>
@@ -573,39 +569,39 @@
           <t>2-6 settimane</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>SAP, Oracle, Microsoft Dynamics</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Leader di mercato, molto completo, ottimo per aziende strutturate</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Conexiom</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>OMS AI dedicato</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>30-300</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>€ 600-2.200</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2-4 settimane</t>
         </is>
@@ -617,11 +613,11 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Focus specifico sull'estrazione dati da PDF/email ordine</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
+          <t>Focus sull'estrazione dati da PDF/email d'ordine</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>HighRadius</t>
@@ -647,39 +643,39 @@
           <t>4-8 settimane</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>SAP, Oracle, Microsoft</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Copre tutto il ciclo O2C (dall'ordine al recupero crediti)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Copre tutto il ciclo O2C, dall'ordine al recupero crediti</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>UiPath + Document AI</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>RPA + AI sopra ERP</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>RPA + AI sopra l'ERP</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>30-200</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>€ 400-1.200</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>3-6 settimane</t>
         </is>
@@ -691,11 +687,11 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Flessibile, serve partner certificato per setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="52" customHeight="1">
+          <t>Flessibile, serve un partner certificato per il setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Automation Anywhere</t>
@@ -703,7 +699,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>RPA + AI sopra ERP</t>
+          <t>RPA + AI sopra l'ERP</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -721,39 +717,39 @@
           <t>3-6 settimane</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Qualsiasi ERP</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Simile a UiPath, ottimo marketplace di bot preconfezionati</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Simile a UiPath, ottimo marketplace di bot pronti</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Blue Prism</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>RPA + AI sopra ERP</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>RPA + AI sopra l'ERP</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>100+</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>€ 800+</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>4-8 settimane</t>
         </is>
@@ -765,11 +761,11 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Enterprise-grade, serve IT strutturato internamente</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
+          <t>Enterprise-grade, serve un IT strutturato interno</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Make.com + OpenAI API</t>
@@ -795,39 +791,39 @@
           <t>1-3 giornate</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Via API / webhook</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Budget minimo, flessibile, richiede consulente Make-oriented</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Budget minimo, flessibile, richiede un consulente Make</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>n8n (self-hosted) + OpenAI</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Low-code open source</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>5-80</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>€ 30-150</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>2-5 giornate</t>
         </is>
@@ -843,7 +839,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
+    <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Zapier + Claude API</t>
@@ -869,39 +865,39 @@
           <t>1-2 giornate</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Limitata sugli ERP italiani</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Semplicissimo, ma meno potente di Make/n8n</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Zucchetti Infinity + AI</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>ERP italiano con moduli AI</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>20-200</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Su preventivo</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>4-12 settimane</t>
         </is>
@@ -917,7 +913,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>TeamSystem + AI</t>
@@ -943,39 +939,39 @@
           <t>4-12 settimane</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Nativo</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Stessa logica di Zucchetti, buon supporto italiano</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Mago.net + estensioni</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>ERP italiano con add-on</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>10-100</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Su preventivo</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>3-8 settimane</t>
         </is>
@@ -987,15 +983,11 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Molto usato in Italia nelle PMI, AI via partner certificati</t>
+          <t>Molto usato in Italia, AI tramite partner certificati</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1010,21 +1002,21 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AIOsha · 20 domande da fare al vendor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>AI Osha — 20 domande da fare al vendor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prima di firmare contratto O2C</t>
+          <t>Prima di firmare un contratto Order-to-Cash.</t>
         </is>
       </c>
     </row>
@@ -1045,203 +1037,195 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>DATI &amp; PRIVACY</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Dove vengono conservati i dati estratti dagli ordini (UE / extra-UE)?</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>DATI &amp; PRIVACY</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Avete DPA (Data Processing Agreement) pronto e conforme GDPR?</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+          <t>Avete un DPA (Data Processing Agreement) pronto e conforme al GDPR?</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>DATI &amp; PRIVACY</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>I miei dati vengono usati per addestramento del modello?</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>I miei dati vengono usati per addestrare il modello?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>ACCURATEZZA</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Qual è la percentuale media di estrazione corretta su PDF ordine?</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+          <t>Qual è la percentuale media di estrazione corretta da un PDF d'ordine?</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>ACCURATEZZA</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Come viene gestito un ordine con codice prodotto sconosciuto?</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Come viene gestito un ordine con un codice prodotto sconosciuto?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>ACCURATEZZA</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Posso definire regole custom di mapping codici cliente → miei?</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+          <t>Posso definire regole personalizzate di mapping codici cliente verso i miei?</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>INTEGRAZIONE</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Avete integrazione nativa con il mio ERP (specificare quale)?</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Avete un'integrazione nativa con il mio ERP (specificare quale)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>INTEGRAZIONE</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Servono sviluppi custom? Se sì, a che prezzo?</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+          <t>Servono sviluppi su misura? Se sì, a che prezzo?</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>INTEGRAZIONE</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Tempistica realistica di go-live end-to-end?</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Qual è la tempistica realistica di go-live end-to-end?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>COSTI</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Canone fisso o a consumo? Unità di misura (ordine / riga / documento)?</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+          <t>Canone fisso o a consumo? Con quale unità di misura (ordine / riga / documento)?</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>COSTI</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Costo di setup / onboarding iniziale?</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Qual è il costo di setup / onboarding iniziale?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>COSTI</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Cosa succede se i volumi scendono (sotto il minimo)?</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+          <t>Cosa succede se i volumi scendono sotto il minimo?</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>SUPPORTO</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>SLA di supporto (tempo di risposta, canale)?</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Quali sono gli SLA di supporto (tempo di risposta, canale)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>SUPPORTO</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Supporto in italiano o solo in inglese?</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+          <t>Il supporto è in italiano o solo in inglese?</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>SUPPORTO</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Chi gestisce la formazione dei miei operatori?</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>USCITA</t>
         </is>
@@ -1251,49 +1235,47 @@
           <t>Posso esportare tutti i miei dati storici in caso di recesso?</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="C20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>USCITA</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Durata minima del contratto? Disdetta preavviso?</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Qual è la durata minima del contratto e il preavviso di disdetta?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>USCITA</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Procedura di migrazione verso altro vendor (se necessario)?</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+          <t>Qual è la procedura di migrazione verso un altro vendor?</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>REFERENZE</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Posso parlare con 2-3 PMI italiane già vostri clienti?</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Posso parlare con 2-3 aziende italiane già vostre clienti?</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>REFERENZE</t>
         </is>
@@ -1303,13 +1285,9 @@
           <t>Avete case study specifici sul mio settore?</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
+      <c r="C24" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1320,25 +1298,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AIOsha · Business case Order-to-Cash AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>AI Osha — Business case Order-to-Cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Calcolo ROI per presentazione al CdA</t>
+          <t>Compila i valori in giallo: ROI e risparmi si calcolano da soli.</t>
         </is>
       </c>
     </row>
@@ -1360,288 +1338,246 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Numero ordini al giorno</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="9" t="n">
         <v>80</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Numero ordini totali arrivati / giorno lavorativo</t>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Ordini totali arrivati per giorno lavorativo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Tempo medio inserimento manuale (minuti)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Tempo reale osservato nel team</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Giorni lavorativi all'anno</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="9" t="n">
         <v>220</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Standard IT per PMI</t>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Standard per l'Italia</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Costo orario medio operatore (€)</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Lordo aziendale</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Costo annuo attuale data entry (€)</t>
         </is>
       </c>
-      <c r="B9" s="6">
-        <f>B5*B6*B7/60*B8</f>
+      <c r="B9">
+        <f>B5*B6*B7*B8/60</f>
         <v/>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Calcolato: ordini × min × giorni × €/ora / 60</t>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>ordini x minuti x giorni x €/ora / 60</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>% riduzione attesa con l'AI</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Tipico 60-90% a regime</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>% riduzione post-AI</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Tipico 60-90% a regime</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Risparmio annuo lordo (€)</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>B9*B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Costo attuale x % riduzione</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Risparmio annuo lordo (€)</t>
-        </is>
-      </c>
-      <c r="B12" s="6">
-        <f>B10*B9</f>
-        <v/>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Calcolato</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Canone mensile soluzione (€)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Da preventivo vendor</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Canone mensile soluzione (€)</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Setup una-tantum (€)</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Da preventivo vendor</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Setup una-tantum (€)</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Da preventivo vendor</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Costo anno 1 (€)</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B14">
         <f>B12*12+B13</f>
         <v/>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Canone × 12 + setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Canone x 12 + setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Risparmio netto anno 1 (€)</t>
         </is>
       </c>
-      <c r="B16" s="6">
+      <c r="B15" s="12">
         <f>B11-B14</f>
         <v/>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Risparmio - Costi</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Risparmio lordo - costo anno 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>ROI % anno 1</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>B15/B14</f>
+      <c r="B16" s="13">
+        <f>IF(B14=0,0,B15/B14)</f>
         <v/>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>In percentuale</t>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Risparmio netto / costo anno 1</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="4" t="inlineStr"/>
-      <c r="C18" s="5" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Benefici non monetizzati (da elencare nel documento):</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Benefici non monetizzati</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Elencali nel documento:</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Errori di spedizione</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>-70/90%: meno resi e meno sconti commerciali</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Errori di spedizione</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>-70/90%</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Minor reso, minor discount commerciale</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Tempo medio di consegna</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>-1/-2 giorni: miglior NPS, più ordini ripetuti</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Tempo medio consegna</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>-1/-2 giorni</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Miglior NPS cliente, più ordini ripetuti</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Turnover ufficio ordini</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>-30/50%: le persone fanno un lavoro più interessante</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Turnover ufficio ordini</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>-30/50%</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Persone fanno lavoro più interessante</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → Rischio su scadenze PEC</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Se hai integrazione PEC, meno contenziosi</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Rischio su scadenze PEC</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>con integrazione PEC, meno contenziosi</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>